--- a/data/GameContent_Perks_Worldbosses.xlsx
+++ b/data/GameContent_Perks_Worldbosses.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R90a016cf443c4b37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="2" r:id="R4aeaea5cd8f34e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses" sheetId="3" r:id="R82f34d189b594434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Minions" sheetId="4" r:id="Re315a664fb7d4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="5" r:id="R754ec64be23d40ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor" sheetId="6" r:id="Rc91994e967fe4636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpecialItems" sheetId="7" r:id="R40c1283c62db4c99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="8" r:id="Rbebbb7599e3240fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomEvents" sheetId="9" r:id="Rdaf7934f72324a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="10" r:id="R63946441410e476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorldBosses" sheetId="11" r:id="R746c8243db70409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perks" sheetId="13" r:id="R6e26a05292fc468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="14" r:id="R12e122eb7e424ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="Rb07bc4dda674430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SceneChoices" sheetId="16" r:id="R85bdd64d30a24d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0d67bf003e1e4599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="2" r:id="R8fabb0102b0d475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses" sheetId="3" r:id="R14899aa2d8024959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Minions" sheetId="4" r:id="R40f68701e32f4c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="5" r:id="R3f300a237e964d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor" sheetId="6" r:id="R9d0e1b31309b4cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpecialItems" sheetId="7" r:id="R516ff376aed14f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="8" r:id="R72b19fa947ce41d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomEvents" sheetId="9" r:id="Rdbc0cd66b3cd48f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="10" r:id="R40bf9a9bfe194fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorldBosses" sheetId="11" r:id="R61c806e6073343be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perks" sheetId="13" r:id="Rd21ca79c6fff4fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="14" r:id="R4cd19f5a8e164729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="Re1ac750bdeb04b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SceneChoices" sheetId="16" r:id="Re1f7ea3828d148c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,7 +519,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenesTable" displayName="ScenesTable" ref="A1:T35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenesTable" displayName="ScenesTable" ref="A1:T52" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="20">
     <x:tableColumn id="1" name="SceneKey"/>
     <x:tableColumn id="2" name="MovieName"/>
@@ -547,7 +547,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SceneChoicesTable" displayName="SceneChoicesTable" ref="A1:P171" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SceneChoicesTable" displayName="SceneChoicesTable" ref="A1:P256" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="SceneKey"/>
     <x:tableColumn id="2" name="ChoiceKey"/>
@@ -6836,10 +6836,10 @@
         <x:v>Highlander</x:v>
       </x:c>
       <x:c r="C11" s="66" t="str">
-        <x:v>Steel Beneath the City</x:v>
+        <x:v>The Madison Square Garage</x:v>
       </x:c>
       <x:c r="D11" s="66" t="str">
-        <x:v>An underground garage rings with the scrape of drawn steel. Connor MacLeod recognizes the stance of a Hired Sword blocking the only ramp to the street.</x:v>
+        <x:v>The wrestling crowd has emptied into the night, leaving Madison Square Garden's parking garage to echo with tire squeals and distant laughter. Connor MacLeod hears another blade clear its sheath as a cackling swordsman cartwheels between the parked cars.</x:v>
       </x:c>
       <x:c r="E11" s="66" t="str">
         <x:v>Connor MacLeod</x:v>
@@ -8378,10 +8378,1064 @@
         <x:v>Late-game arena Scene against the Harkonnen champion.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B36" s="66" t="str">
+        <x:v>Total Recall</x:v>
+      </x:c>
+      <x:c r="C36" s="66" t="str">
+        <x:v>Pursuit Through Venusville</x:v>
+      </x:c>
+      <x:c r="D36" s="66" t="str">
+        <x:v>Neon signs and red dust crowd the alleys of Venusville as Richter's men close every route to the Last Resort. Douglas Quaid pulls Melina toward the mutant tunnels while Richter enters the district with a pistol and orders to bring back Quaid's body.</x:v>
+      </x:c>
+      <x:c r="E36" s="66" t="str">
+        <x:v>Douglas Quaid</x:v>
+      </x:c>
+      <x:c r="F36" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G36" s="66" t="str">
+        <x:v>Richter</x:v>
+      </x:c>
+      <x:c r="H36" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I36" s="73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J36" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K36" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L36" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M36" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N36" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P36" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q36" s="73" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="R36" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S36" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T36" s="66" t="str">
+        <x:v>Minion Scene combining uncertain memories with a clinic pursuit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="48" customHeight="1">
+      <x:c r="A37" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B37" s="66" t="str">
+        <x:v>Star Trek VI: The Undiscovered Country</x:v>
+      </x:c>
+      <x:c r="C37" s="66" t="str">
+        <x:v>The Logic of Betrayal</x:v>
+      </x:c>
+      <x:c r="D37" s="66" t="str">
+        <x:v>The Enterprise computer has exposed a trail of altered torpedo records, missing gravity boots, and conspirators aboard both ships. Spock seals the briefing room while Kirk confronts Valeris, whose perfect Vulcan composure is beginning to fracture.</x:v>
+      </x:c>
+      <x:c r="E37" s="66" t="str">
+        <x:v>James T. Kirk</x:v>
+      </x:c>
+      <x:c r="F37" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G37" s="66" t="str">
+        <x:v>Valeris</x:v>
+      </x:c>
+      <x:c r="H37" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I37" s="73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J37" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K37" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L37" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M37" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N37" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O37" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P37" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q37" s="73" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="R37" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S37" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T37" s="66" t="str">
+        <x:v>Investigation Scene aboard the Enterprise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B38" s="66" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C38" s="66" t="str">
+        <x:v>Immortals in the Dark</x:v>
+      </x:c>
+      <x:c r="D38" s="66" t="str">
+        <x:v>The moon disappears behind smoke as masked warriors climb over the bodies at the pass. Leonidas lowers his spear while a Persian Immortal moves silently toward the broken shield wall.</x:v>
+      </x:c>
+      <x:c r="E38" s="66" t="str">
+        <x:v>Leonidas</x:v>
+      </x:c>
+      <x:c r="F38" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G38" s="66" t="str">
+        <x:v>Persian Immortal</x:v>
+      </x:c>
+      <x:c r="H38" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I38" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J38" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K38" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L38" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M38" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N38" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O38" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P38" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q38" s="73" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="R38" s="73" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S38" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T38" s="66" t="str">
+        <x:v>Night assault by Xerxes's elite minion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="48" customHeight="1">
+      <x:c r="A39" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B39" s="66" t="str">
+        <x:v>Terminator 2: Judgment Day</x:v>
+      </x:c>
+      <x:c r="C39" s="66" t="str">
+        <x:v>Los Angeles, 2029</x:v>
+      </x:c>
+      <x:c r="D39" s="66" t="str">
+        <x:v>Hunter-Killer searchlights rake across a field of human skulls while plasma fire turns the ruined freeway blue-white. Sarah Connor's warning echoes over the resistance channel as a bare T-800 Endoskeleton steps through the flames and locks its red optic onto the survivors.</x:v>
+      </x:c>
+      <x:c r="E39" s="66" t="str">
+        <x:v>Sarah Connor</x:v>
+      </x:c>
+      <x:c r="F39" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G39" s="66" t="str">
+        <x:v>T-800 Endoskeleton</x:v>
+      </x:c>
+      <x:c r="H39" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I39" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J39" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K39" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L39" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M39" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N39" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P39" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q39" s="73" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="R39" s="73" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S39" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T39" s="66" t="str">
+        <x:v>Future-war minion encounter on a ruined freeway.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="48" customHeight="1">
+      <x:c r="A40" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B40" s="66" t="str">
+        <x:v>The Lord of the Rings: The Two Towers</x:v>
+      </x:c>
+      <x:c r="C40" s="66" t="str">
+        <x:v>Breach at the Deeping Wall</x:v>
+      </x:c>
+      <x:c r="D40" s="66" t="str">
+        <x:v>Rain lashes the fortress as ladders rise against the stone. Aragorn reaches the shattered parapet while an Uruk-hai Berserker charges through the smoke.</x:v>
+      </x:c>
+      <x:c r="E40" s="66" t="str">
+        <x:v>Aragorn</x:v>
+      </x:c>
+      <x:c r="F40" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G40" s="66" t="str">
+        <x:v>Uruk-hai Berserker</x:v>
+      </x:c>
+      <x:c r="H40" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I40" s="73" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J40" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K40" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L40" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M40" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N40" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P40" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q40" s="73" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R40" s="73" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S40" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T40" s="66" t="str">
+        <x:v>Helm's Deep minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B41" s="66" t="str">
+        <x:v>The Matrix</x:v>
+      </x:c>
+      <x:c r="C41" s="66" t="str">
+        <x:v>Agent on the Rooftop</x:v>
+      </x:c>
+      <x:c r="D41" s="66" t="str">
+        <x:v>Helicopter rotors beat against a glass tower while green code ripples across the skyline. Neo reaches the roof as Agent Jones takes control of a nearby guard.</x:v>
+      </x:c>
+      <x:c r="E41" s="66" t="str">
+        <x:v>Neo</x:v>
+      </x:c>
+      <x:c r="F41" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G41" s="66" t="str">
+        <x:v>Agent Jones</x:v>
+      </x:c>
+      <x:c r="H41" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I41" s="73" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J41" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K41" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L41" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M41" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N41" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O41" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P41" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q41" s="73" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R41" s="73" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S41" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T41" s="66" t="str">
+        <x:v>Rooftop minion confrontation inside the Matrix.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="48" customHeight="1">
+      <x:c r="A42" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B42" s="66" t="str">
+        <x:v>Gladiator</x:v>
+      </x:c>
+      <x:c r="C42" s="66" t="str">
+        <x:v>The Tigers of Carthage</x:v>
+      </x:c>
+      <x:c r="D42" s="66" t="str">
+        <x:v>Trapdoors open beneath the Colosseum sand and chained tigers lunge at the limits of their handlers' reach. Maximus raises his shield as Tigris of Gaul advances in engraved armor, fighting for the crowd and for Commodus watching from the imperial box.</x:v>
+      </x:c>
+      <x:c r="E42" s="66" t="str">
+        <x:v>Maximus</x:v>
+      </x:c>
+      <x:c r="F42" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G42" s="66" t="str">
+        <x:v>Tigris of Gaul</x:v>
+      </x:c>
+      <x:c r="H42" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I42" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J42" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K42" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L42" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M42" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N42" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P42" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q42" s="73" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="R42" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="S42" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T42" s="66" t="str">
+        <x:v>Arena minion Scene against the celebrated champion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="48" customHeight="1">
+      <x:c r="A43" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B43" s="66" t="str">
+        <x:v>The Thing</x:v>
+      </x:c>
+      <x:c r="C43" s="66" t="str">
+        <x:v>Blair's Tool Shed</x:v>
+      </x:c>
+      <x:c r="D43" s="66" t="str">
+        <x:v>The tractor, radio equipment, and remaining escape routes have been methodically ruined. MacReady follows a trail through the snow to Blair's tool shed, where an infected crewman stands among scavenged machine parts and an unfinished shape that was never built by human hands.</x:v>
+      </x:c>
+      <x:c r="E43" s="66" t="str">
+        <x:v>MacReady</x:v>
+      </x:c>
+      <x:c r="F43" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G43" s="66" t="str">
+        <x:v>Infected Crewman</x:v>
+      </x:c>
+      <x:c r="H43" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I43" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J43" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K43" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L43" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M43" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N43" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P43" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q43" s="73" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="R43" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="S43" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T43" s="66" t="str">
+        <x:v>Suspicion-driven minion Scene outside Outpost 31.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="48" customHeight="1">
+      <x:c r="A44" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B44" s="66" t="str">
+        <x:v>Star Wars: The Empire Strikes Back</x:v>
+      </x:c>
+      <x:c r="C44" s="66" t="str">
+        <x:v>Escape from Echo Base</x:v>
+      </x:c>
+      <x:c r="D44" s="66" t="str">
+        <x:v>Ice dust falls from the ceiling as warning sirens echo through the rebel base. Luke Skywalker reaches the hangar route while an Imperial Stormtrooper squad leader blocks the corridor.</x:v>
+      </x:c>
+      <x:c r="E44" s="66" t="str">
+        <x:v>Luke Skywalker</x:v>
+      </x:c>
+      <x:c r="F44" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G44" s="66" t="str">
+        <x:v>Imperial Stormtrooper</x:v>
+      </x:c>
+      <x:c r="H44" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I44" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J44" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K44" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L44" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M44" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N44" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O44" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P44" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q44" s="73" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R44" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="S44" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T44" s="66" t="str">
+        <x:v>Echo Base evacuation minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="48" customHeight="1">
+      <x:c r="A45" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B45" s="66" t="str">
+        <x:v>Flash Gordon</x:v>
+      </x:c>
+      <x:c r="C45" s="66" t="str">
+        <x:v>Trial Before Prince Vultan</x:v>
+      </x:c>
+      <x:c r="D45" s="66" t="str">
+        <x:v>The feast hall of Sky City shakes with laughter as Prince Vultan's Hawkmen debate whether an Earthman is worth following into war against Ming. A Hawkman champion sweeps onto the landing bridge and challenges Flash Gordon to prove his courage before the entire winged court.</x:v>
+      </x:c>
+      <x:c r="E45" s="66" t="str">
+        <x:v>Flash Gordon</x:v>
+      </x:c>
+      <x:c r="F45" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G45" s="66" t="str">
+        <x:v>Hawkman</x:v>
+      </x:c>
+      <x:c r="H45" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I45" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J45" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K45" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L45" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M45" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N45" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O45" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P45" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q45" s="73" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R45" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="S45" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T45" s="66" t="str">
+        <x:v>Aerial minion challenge over Sky City.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="48" customHeight="1">
+      <x:c r="A46" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B46" s="66" t="str">
+        <x:v>Willow</x:v>
+      </x:c>
+      <x:c r="C46" s="66" t="str">
+        <x:v>The Gate of Nockmaar</x:v>
+      </x:c>
+      <x:c r="D46" s="66" t="str">
+        <x:v>Rain runs black over the fortress stones as chains rattle above the moat. Willow Ufgood reaches the gate controls while a Nockmaar Soldier descends the stair with sword raised.</x:v>
+      </x:c>
+      <x:c r="E46" s="66" t="str">
+        <x:v>Willow Ufgood</x:v>
+      </x:c>
+      <x:c r="F46" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G46" s="66" t="str">
+        <x:v>Nockmaar Soldier</x:v>
+      </x:c>
+      <x:c r="H46" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I46" s="73" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J46" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K46" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L46" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M46" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N46" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P46" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q46" s="73" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R46" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="S46" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T46" s="66" t="str">
+        <x:v>Fortress infiltration minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="48" customHeight="1">
+      <x:c r="A47" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B47" s="66" t="str">
+        <x:v>Labyrinth</x:v>
+      </x:c>
+      <x:c r="C47" s="66" t="str">
+        <x:v>The Door That Wasn't There</x:v>
+      </x:c>
+      <x:c r="D47" s="66" t="str">
+        <x:v>A blank wall opens onto a corridor crowded with mismatched doors. Sarah Williams chooses a path while a Goblin Guard drags a club around the nearest corner.</x:v>
+      </x:c>
+      <x:c r="E47" s="66" t="str">
+        <x:v>Sarah Williams</x:v>
+      </x:c>
+      <x:c r="F47" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G47" s="66" t="str">
+        <x:v>Goblin Guard</x:v>
+      </x:c>
+      <x:c r="H47" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I47" s="73" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J47" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K47" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L47" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M47" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N47" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O47" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P47" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q47" s="73" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R47" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="S47" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T47" s="66" t="str">
+        <x:v>Maze-navigation minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="48" customHeight="1">
+      <x:c r="A48" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B48" s="66" t="str">
+        <x:v>Tron</x:v>
+      </x:c>
+      <x:c r="C48" s="66" t="str">
+        <x:v>The Disc Arena</x:v>
+      </x:c>
+      <x:c r="D48" s="66" t="str">
+        <x:v>A glowing grid forms beneath the prisoners as walls rise around the arena. Kevin Flynn catches an identity disc while Sark steps onto the opposite platform.</x:v>
+      </x:c>
+      <x:c r="E48" s="66" t="str">
+        <x:v>Kevin Flynn</x:v>
+      </x:c>
+      <x:c r="F48" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G48" s="66" t="str">
+        <x:v>Sark</x:v>
+      </x:c>
+      <x:c r="H48" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I48" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J48" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K48" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L48" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M48" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N48" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O48" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P48" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q48" s="73" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R48" s="73" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="S48" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T48" s="66" t="str">
+        <x:v>Digital arena minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="48" customHeight="1">
+      <x:c r="A49" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B49" s="66" t="str">
+        <x:v>Army of Darkness</x:v>
+      </x:c>
+      <x:c r="C49" s="66" t="str">
+        <x:v>The Graveyard Awakens</x:v>
+      </x:c>
+      <x:c r="D49" s="66" t="str">
+        <x:v>Moonlight cuts across crooked stones as skeletal hands break through the soil. Ash Williams raises his boomstick while a Deadite Warrior claws free beside the open grave.</x:v>
+      </x:c>
+      <x:c r="E49" s="66" t="str">
+        <x:v>Ash Williams</x:v>
+      </x:c>
+      <x:c r="F49" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G49" s="66" t="str">
+        <x:v>Deadite Warrior</x:v>
+      </x:c>
+      <x:c r="H49" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I49" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J49" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K49" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L49" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M49" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N49" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O49" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P49" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q49" s="73" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R49" s="73" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="S49" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T49" s="66" t="str">
+        <x:v>Graveyard minion Scene with improvised slapstick hazards.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
+      <x:c r="A50" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B50" s="66" t="str">
+        <x:v>Stargate</x:v>
+      </x:c>
+      <x:c r="C50" s="66" t="str">
+        <x:v>The Horus Gate</x:v>
+      </x:c>
+      <x:c r="D50" s="66" t="str">
+        <x:v>Sunlight cuts through the temple doorway as villagers scatter across the courtyard. Daniel Jackson reaches the symbol wall while a Horus Guard lowers its staff weapon.</x:v>
+      </x:c>
+      <x:c r="E50" s="66" t="str">
+        <x:v>Daniel Jackson</x:v>
+      </x:c>
+      <x:c r="F50" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G50" s="66" t="str">
+        <x:v>Horus Guard</x:v>
+      </x:c>
+      <x:c r="H50" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I50" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J50" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K50" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L50" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M50" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N50" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O50" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P50" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q50" s="73" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="R50" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="S50" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T50" s="66" t="str">
+        <x:v>Temple uprising minion Scene.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
+      <x:c r="A51" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B51" s="66" t="str">
+        <x:v>Excalibur</x:v>
+      </x:c>
+      <x:c r="C51" s="66" t="str">
+        <x:v>Challenge at the Ford</x:v>
+      </x:c>
+      <x:c r="D51" s="66" t="str">
+        <x:v>Morning mist hangs over a flooded ford where a black-armored knight has planted his banner and barred the road to Camelot. King Arthur rides forward beneath the dragon standard as the Black Knight lowers a lance and demands trial by arms.</x:v>
+      </x:c>
+      <x:c r="E51" s="66" t="str">
+        <x:v>King Arthur</x:v>
+      </x:c>
+      <x:c r="F51" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G51" s="66" t="str">
+        <x:v>Black Knight</x:v>
+      </x:c>
+      <x:c r="H51" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I51" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J51" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K51" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L51" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M51" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N51" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O51" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P51" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q51" s="73" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="R51" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="S51" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T51" s="66" t="str">
+        <x:v>Chivalric minion duel at a guarded crossing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="48" customHeight="1">
+      <x:c r="A52" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B52" s="66" t="str">
+        <x:v>Dune 2021</x:v>
+      </x:c>
+      <x:c r="C52" s="66" t="str">
+        <x:v>Raid Beneath the Sand</x:v>
+      </x:c>
+      <x:c r="D52" s="66" t="str">
+        <x:v>Ornithopter wreckage burns beneath a moonless sky as blades move through the dust. Paul Atreides draws his crysknife while a Sardaukar Trooper descends the dune.</x:v>
+      </x:c>
+      <x:c r="E52" s="66" t="str">
+        <x:v>Paul Atreides</x:v>
+      </x:c>
+      <x:c r="F52" s="66" t="str">
+        <x:v>MINION</x:v>
+      </x:c>
+      <x:c r="G52" s="66" t="str">
+        <x:v>Sardaukar Trooper</x:v>
+      </x:c>
+      <x:c r="H52" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I52" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J52" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K52" s="66" t="str">
+        <x:v>DEFEAT_ENEMY</x:v>
+      </x:c>
+      <x:c r="L52" s="66" t="str">
+        <x:v>ATTACK_ONLY</x:v>
+      </x:c>
+      <x:c r="M52" s="66" t="str">
+        <x:v>THREAT_WEIGHTED</x:v>
+      </x:c>
+      <x:c r="N52" s="67" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O52" s="74" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="P52" s="74" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q52" s="73" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R52" s="73" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="S52" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T52" s="66" t="str">
+        <x:v>Desert minion ambush against an elite trooper.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fb6d1e548214eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb46372997334728"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10719,16 +11773,16 @@
         <x:v>STR</x:v>
       </x:c>
       <x:c r="D47" s="66" t="str">
-        <x:v>Push an abandoned car into the duelist's escape route.</x:v>
+        <x:v>Rip the parking barrier from its mount and sweep the swordsman's legs.</x:v>
       </x:c>
       <x:c r="E47" s="73" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="66" t="str">
-        <x:v>The vehicle rolls across the ramp and traps the Hired Sword in Connor's reach.</x:v>
+        <x:v>The barrier catches him between two cars and leaves his guard open to Connor.</x:v>
       </x:c>
       <x:c r="G47" s="66" t="str">
-        <x:v>The parking brake catches and the duelist charges while you strain against it.</x:v>
+        <x:v>He vaults the barrier, laughing, and lands inside your reach.</x:v>
       </x:c>
       <x:c r="H47" s="73" t="n">
         <x:v>38</x:v>
@@ -10769,16 +11823,16 @@
         <x:v>END</x:v>
       </x:c>
       <x:c r="D48" s="66" t="str">
-        <x:v>Absorb the first rush and hold the narrow lane for Connor.</x:v>
+        <x:v>Weather his manic series of cuts until the garage sprinklers obscure his sight.</x:v>
       </x:c>
       <x:c r="E48" s="73" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="66" t="str">
-        <x:v>You withstand the assault and give Connor room to counterattack.</x:v>
+        <x:v>You refuse to break while water and sparks ruin his rhythm.</x:v>
       </x:c>
       <x:c r="G48" s="66" t="str">
-        <x:v>The sustained attack drives you backward into a concrete pillar.</x:v>
+        <x:v>His blade finds you before the sprinklers can hide your position.</x:v>
       </x:c>
       <x:c r="H48" s="73" t="n">
         <x:v>40</x:v>
@@ -10819,16 +11873,16 @@
         <x:v>AGI</x:v>
       </x:c>
       <x:c r="D49" s="66" t="str">
-        <x:v>Vault the divider and close from the duelist's blind side.</x:v>
+        <x:v>Vault a car hood as he cartwheels into another slashing pass.</x:v>
       </x:c>
       <x:c r="E49" s="73" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F49" s="66" t="str">
-        <x:v>You land behind the Hired Sword and force him to split his attention.</x:v>
+        <x:v>You clear the blade and land beside Connor with room to counter.</x:v>
       </x:c>
       <x:c r="G49" s="66" t="str">
-        <x:v>Your boot clips the rail and announces the maneuver.</x:v>
+        <x:v>Your boot slips on the polished hood and he turns beneath you.</x:v>
       </x:c>
       <x:c r="H49" s="73" t="n">
         <x:v>37</x:v>
@@ -10869,16 +11923,16 @@
         <x:v>LCK</x:v>
       </x:c>
       <x:c r="D50" s="66" t="str">
-        <x:v>Strike a random vehicle and trust its alarm to hide your movement.</x:v>
+        <x:v>Strike a car alarm and trust the echo to disguise Connor's approach.</x:v>
       </x:c>
       <x:c r="E50" s="73" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F50" s="66" t="str">
-        <x:v>A chorus of alarms erupts and masks Connor's approach.</x:v>
+        <x:v>Every alarm on the level erupts, swallowing Connor's footsteps.</x:v>
       </x:c>
       <x:c r="G50" s="66" t="str">
-        <x:v>Only one weak horn sounds, pointing directly to your position.</x:v>
+        <x:v>Only one horn answers, pointing directly to your position.</x:v>
       </x:c>
       <x:c r="H50" s="73" t="n">
         <x:v>46</x:v>
@@ -10919,16 +11973,16 @@
         <x:v>PER</x:v>
       </x:c>
       <x:c r="D51" s="66" t="str">
-        <x:v>Use windshields and mirrors to track the duelist's footwork.</x:v>
+        <x:v>Separate his footfalls from their echoes among the concrete pillars.</x:v>
       </x:c>
       <x:c r="E51" s="73" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F51" s="66" t="str">
-        <x:v>The reflections reveal his intended lunge before it begins.</x:v>
+        <x:v>You identify the real approach before his blade appears around the pillar.</x:v>
       </x:c>
       <x:c r="G51" s="66" t="str">
-        <x:v>A shattered mirror feeds you a false angle.</x:v>
+        <x:v>A spinning hubcap supplies the wrong echo and draws your eyes away.</x:v>
       </x:c>
       <x:c r="H51" s="73" t="n">
         <x:v>39</x:v>
@@ -16958,10 +18012,4260 @@
         <x:v>Perception is favored.</x:v>
       </x:c>
     </x:row>
+    <x:row r="172" ht="48" customHeight="1">
+      <x:c r="A172" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B172" s="66" t="str">
+        <x:v>BREAK_SHUTTER</x:v>
+      </x:c>
+      <x:c r="C172" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D172" s="66" t="str">
+        <x:v>Force open the service hatch behind the Last Resort before Richter seals the block.</x:v>
+      </x:c>
+      <x:c r="E172" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F172" s="66" t="str">
+        <x:v>The hatch tears free and Quaid gets Melina into the mutant tunnels.</x:v>
+      </x:c>
+      <x:c r="G172" s="66" t="str">
+        <x:v>The warped frame jams halfway and Richter reaches the alley.</x:v>
+      </x:c>
+      <x:c r="H172" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I172" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J172" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K172" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L172" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M172" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N172" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O172" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P172" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="48" customHeight="1">
+      <x:c r="A173" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B173" s="66" t="str">
+        <x:v>IGNORE_IMPLANT</x:v>
+      </x:c>
+      <x:c r="C173" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D173" s="66" t="str">
+        <x:v>Push through Venusville's failing air while guiding the wounded toward cover.</x:v>
+      </x:c>
+      <x:c r="E173" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F173" s="66" t="str">
+        <x:v>You keep moving through the thin air and reach Kuato's hidden route.</x:v>
+      </x:c>
+      <x:c r="G173" s="66" t="str">
+        <x:v>The pressure drop buckles your knees as Richter's boots enter the street.</x:v>
+      </x:c>
+      <x:c r="H173" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I173" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J173" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K173" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L173" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M173" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N173" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O173" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P173" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="48" customHeight="1">
+      <x:c r="A174" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B174" s="66" t="str">
+        <x:v>SLIDE_LAB</x:v>
+      </x:c>
+      <x:c r="C174" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D174" s="66" t="str">
+        <x:v>Dive across the Last Resort bar as Richter's first shots shatter the bottles.</x:v>
+      </x:c>
+      <x:c r="E174" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F174" s="66" t="str">
+        <x:v>You slide behind the mirrored counter and emerge on Richter's flank.</x:v>
+      </x:c>
+      <x:c r="G174" s="66" t="str">
+        <x:v>Broken glass catches your hand and kills your momentum.</x:v>
+      </x:c>
+      <x:c r="H174" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I174" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J174" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K174" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L174" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M174" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N174" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O174" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P174" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="48" customHeight="1">
+      <x:c r="A175" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B175" s="66" t="str">
+        <x:v>TRUST_MEMORY</x:v>
+      </x:c>
+      <x:c r="C175" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D175" s="66" t="str">
+        <x:v>Follow a mutant child through an unmarked curtain and trust that it leads below.</x:v>
+      </x:c>
+      <x:c r="E175" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F175" s="66" t="str">
+        <x:v>The curtain hides a service stair into the resistance tunnels.</x:v>
+      </x:c>
+      <x:c r="G175" s="66" t="str">
+        <x:v>It opens into a locked dressing room with Richter outside.</x:v>
+      </x:c>
+      <x:c r="H175" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I175" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J175" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K175" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L175" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M175" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N175" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O175" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P175" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="48" customHeight="1">
+      <x:c r="A176" s="66" t="str">
+        <x:v>TOTALRECALL_REKALL_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B176" s="66" t="str">
+        <x:v>READ_CAMERAS</x:v>
+      </x:c>
+      <x:c r="C176" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D176" s="66" t="str">
+        <x:v>Use the mirrored liquor wall to distinguish Richter from his reflections.</x:v>
+      </x:c>
+      <x:c r="E176" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F176" s="66" t="str">
+        <x:v>His muzzle flash reveals the real angle before he clears the doorway.</x:v>
+      </x:c>
+      <x:c r="G176" s="66" t="str">
+        <x:v>A flickering neon sign creates a convincing false flash.</x:v>
+      </x:c>
+      <x:c r="H176" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I176" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J176" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K176" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L176" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M176" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N176" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O176" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P176" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="48" customHeight="1">
+      <x:c r="A177" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B177" s="66" t="str">
+        <x:v>JAM_LIFT</x:v>
+      </x:c>
+      <x:c r="C177" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D177" s="66" t="str">
+        <x:v>Hold the briefing-room doors as conspirators try to retrieve Valeris.</x:v>
+      </x:c>
+      <x:c r="E177" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F177" s="66" t="str">
+        <x:v>The doors remain sealed while Kirk forces the truth into the open.</x:v>
+      </x:c>
+      <x:c r="G177" s="66" t="str">
+        <x:v>The emergency release tears the doors from your grip.</x:v>
+      </x:c>
+      <x:c r="H177" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I177" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J177" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K177" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L177" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M177" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N177" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O177" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P177" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="48" customHeight="1">
+      <x:c r="A178" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B178" s="66" t="str">
+        <x:v>CROSS_STUN_FIRE</x:v>
+      </x:c>
+      <x:c r="C178" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D178" s="66" t="str">
+        <x:v>Remain at the console while Valeris floods it with a nerve-pinch feedback trap.</x:v>
+      </x:c>
+      <x:c r="E178" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F178" s="66" t="str">
+        <x:v>You endure the shock and preserve the altered torpedo records.</x:v>
+      </x:c>
+      <x:c r="G178" s="66" t="str">
+        <x:v>The feedback drives you away and erases part of the evidence.</x:v>
+      </x:c>
+      <x:c r="H178" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I178" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J178" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K178" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L178" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M178" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N178" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O178" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P178" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="48" customHeight="1">
+      <x:c r="A179" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B179" s="66" t="str">
+        <x:v>JEFFERIES_TUBE</x:v>
+      </x:c>
+      <x:c r="C179" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D179" s="66" t="str">
+        <x:v>Reach the equipment locker before Valeris can destroy the magnetic gravity boots.</x:v>
+      </x:c>
+      <x:c r="E179" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F179" s="66" t="str">
+        <x:v>You secure the boots that connect the assassins to Gorkon's ship.</x:v>
+      </x:c>
+      <x:c r="G179" s="66" t="str">
+        <x:v>Valeris seals the locker and cuts off your route.</x:v>
+      </x:c>
+      <x:c r="H179" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I179" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J179" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K179" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L179" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M179" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N179" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O179" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P179" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="48" customHeight="1">
+      <x:c r="A180" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B180" s="66" t="str">
+        <x:v>ISSUE_FALSE_ORDER</x:v>
+      </x:c>
+      <x:c r="C180" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D180" s="66" t="str">
+        <x:v>Search the transporter buffer for one pattern the conspirators failed to purge.</x:v>
+      </x:c>
+      <x:c r="E180" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F180" s="66" t="str">
+        <x:v>A surviving trace identifies the assassins' return to Enterprise.</x:v>
+      </x:c>
+      <x:c r="G180" s="66" t="str">
+        <x:v>The buffer yields a decoy pattern planted for investigators.</x:v>
+      </x:c>
+      <x:c r="H180" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I180" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J180" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K180" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L180" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M180" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N180" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O180" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P180" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="48" customHeight="1">
+      <x:c r="A181" s="66" t="str">
+        <x:v>STARTREKVI_CONSPIRACY</x:v>
+      </x:c>
+      <x:c r="B181" s="66" t="str">
+        <x:v>CHECK_LOGIC</x:v>
+      </x:c>
+      <x:c r="C181" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D181" s="66" t="str">
+        <x:v>Compare Valeris's testimony with the ship's torpedo inventory and Spock's deductions.</x:v>
+      </x:c>
+      <x:c r="E181" s="73" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F181" s="66" t="str">
+        <x:v>One impeccably logical answer contradicts the physical record.</x:v>
+      </x:c>
+      <x:c r="G181" s="66" t="str">
+        <x:v>Her explanation accounts for the discrepancy and conceals the next lie.</x:v>
+      </x:c>
+      <x:c r="H181" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I181" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J181" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K181" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L181" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M181" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N181" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O181" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P181" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="48" customHeight="1">
+      <x:c r="A182" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B182" s="66" t="str">
+        <x:v>RAISE_WALL</x:v>
+      </x:c>
+      <x:c r="C182" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D182" s="66" t="str">
+        <x:v>Lift a fallen shield into the breach beside Leonidas.</x:v>
+      </x:c>
+      <x:c r="E182" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F182" s="66" t="str">
+        <x:v>The shield wall reforms and traps the Immortal in the pass.</x:v>
+      </x:c>
+      <x:c r="G182" s="66" t="str">
+        <x:v>The shield slips and the Immortal attacks through the gap.</x:v>
+      </x:c>
+      <x:c r="H182" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I182" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J182" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K182" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L182" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M182" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N182" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O182" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P182" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="48" customHeight="1">
+      <x:c r="A183" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B183" s="66" t="str">
+        <x:v>HOLD_SPEAR</x:v>
+      </x:c>
+      <x:c r="C183" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D183" s="66" t="str">
+        <x:v>Hold the extended spear line while the Immortal tests it.</x:v>
+      </x:c>
+      <x:c r="E183" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F183" s="66" t="str">
+        <x:v>You withstand the pressure until Leonidas finds an opening.</x:v>
+      </x:c>
+      <x:c r="G183" s="66" t="str">
+        <x:v>Your arms fail and the spear line folds inward.</x:v>
+      </x:c>
+      <x:c r="H183" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I183" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J183" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K183" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L183" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M183" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N183" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O183" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P183" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="48" customHeight="1">
+      <x:c r="A184" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B184" s="66" t="str">
+        <x:v>VAULT_SHIELDS</x:v>
+      </x:c>
+      <x:c r="C184" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D184" s="66" t="str">
+        <x:v>Vault the shield wall and land beyond the Immortal's guard.</x:v>
+      </x:c>
+      <x:c r="E184" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F184" s="66" t="str">
+        <x:v>You land cleanly and turn the masked warrior toward Leonidas.</x:v>
+      </x:c>
+      <x:c r="G184" s="66" t="str">
+        <x:v>The warrior reads the leap and meets you in the air.</x:v>
+      </x:c>
+      <x:c r="H184" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I184" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J184" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K184" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L184" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M184" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N184" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O184" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P184" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="48" customHeight="1">
+      <x:c r="A185" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B185" s="66" t="str">
+        <x:v>THROW_IN_DARK</x:v>
+      </x:c>
+      <x:c r="C185" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D185" s="66" t="str">
+        <x:v>Cast a spear toward the sound of breathing in the dark.</x:v>
+      </x:c>
+      <x:c r="E185" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F185" s="66" t="str">
+        <x:v>The throw tears away the Immortal's mask and ruins the ambush.</x:v>
+      </x:c>
+      <x:c r="G185" s="66" t="str">
+        <x:v>The spear strikes only stone and reveals your position.</x:v>
+      </x:c>
+      <x:c r="H185" s="73" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I185" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J185" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K185" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L185" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M185" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N185" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O185" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P185" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="48" customHeight="1">
+      <x:c r="A186" s="66" t="str">
+        <x:v>THREEHUNDRED_IMMORTAL_NIGHT</x:v>
+      </x:c>
+      <x:c r="B186" s="66" t="str">
+        <x:v>WATCH_DUST</x:v>
+      </x:c>
+      <x:c r="C186" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D186" s="66" t="str">
+        <x:v>Follow disturbed dust beneath the Immortal's silent steps.</x:v>
+      </x:c>
+      <x:c r="E186" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F186" s="66" t="str">
+        <x:v>The dust reveals the attack a heartbeat before it begins.</x:v>
+      </x:c>
+      <x:c r="G186" s="66" t="str">
+        <x:v>Wind across the pass creates a false trail.</x:v>
+      </x:c>
+      <x:c r="H186" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I186" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J186" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K186" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L186" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M186" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N186" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O186" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P186" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="48" customHeight="1">
+      <x:c r="A187" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B187" s="66" t="str">
+        <x:v>TIP_TRUCK</x:v>
+      </x:c>
+      <x:c r="C187" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D187" s="66" t="str">
+        <x:v>Topple a scorched freeway divider into the Endoskeleton's path.</x:v>
+      </x:c>
+      <x:c r="E187" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F187" s="66" t="str">
+        <x:v>The concrete pins one chrome leg beneath the ruins.</x:v>
+      </x:c>
+      <x:c r="G187" s="66" t="str">
+        <x:v>The machine catches the slab and hurls it aside.</x:v>
+      </x:c>
+      <x:c r="H187" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I187" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J187" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K187" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L187" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M187" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N187" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O187" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P187" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="48" customHeight="1">
+      <x:c r="A188" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B188" s="66" t="str">
+        <x:v>CROSS_FIRE</x:v>
+      </x:c>
+      <x:c r="C188" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D188" s="66" t="str">
+        <x:v>Carry a wounded resistance fighter through the Hunter-Killer searchlights.</x:v>
+      </x:c>
+      <x:c r="E188" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F188" s="66" t="str">
+        <x:v>You cross the killing ground without abandoning the survivor.</x:v>
+      </x:c>
+      <x:c r="G188" s="66" t="str">
+        <x:v>A plasma burst throws both of you into the open.</x:v>
+      </x:c>
+      <x:c r="H188" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I188" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J188" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K188" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L188" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M188" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N188" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O188" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P188" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="48" customHeight="1">
+      <x:c r="A189" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B189" s="66" t="str">
+        <x:v>UNDER_WRECK</x:v>
+      </x:c>
+      <x:c r="C189" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D189" s="66" t="str">
+        <x:v>Sprint between the blue sweeps of the aerial Hunter-Killer.</x:v>
+      </x:c>
+      <x:c r="E189" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F189" s="66" t="str">
+        <x:v>You reach the Endoskeleton's blind side between scanning passes.</x:v>
+      </x:c>
+      <x:c r="G189" s="66" t="str">
+        <x:v>The searchlight reverses early and paints you in white.</x:v>
+      </x:c>
+      <x:c r="H189" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I189" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J189" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K189" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L189" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M189" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N189" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O189" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P189" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="48" customHeight="1">
+      <x:c r="A190" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B190" s="66" t="str">
+        <x:v>START_ENGINE</x:v>
+      </x:c>
+      <x:c r="C190" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D190" s="66" t="str">
+        <x:v>Fire an abandoned resistance plasma rifle before its cracked cell overloads.</x:v>
+      </x:c>
+      <x:c r="E190" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F190" s="66" t="str">
+        <x:v>One remaining charge strikes the Endoskeleton squarely in the chest.</x:v>
+      </x:c>
+      <x:c r="G190" s="66" t="str">
+        <x:v>The cell vents in your hands without firing.</x:v>
+      </x:c>
+      <x:c r="H190" s="73" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I190" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J190" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K190" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L190" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M190" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N190" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O190" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P190" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="48" customHeight="1">
+      <x:c r="A191" s="66" t="str">
+        <x:v>T2_FREEWAY_AMBUSH</x:v>
+      </x:c>
+      <x:c r="B191" s="66" t="str">
+        <x:v>TRACK_OPTICS</x:v>
+      </x:c>
+      <x:c r="C191" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D191" s="66" t="str">
+        <x:v>Read the red optic's tracking rhythm against the Hunter-Killer sweep.</x:v>
+      </x:c>
+      <x:c r="E191" s="73" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F191" s="66" t="str">
+        <x:v>You find the instant both machines lose the same patch of roadway.</x:v>
+      </x:c>
+      <x:c r="G191" s="66" t="str">
+        <x:v>Ash in the air makes the optic appear to turn away.</x:v>
+      </x:c>
+      <x:c r="H191" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I191" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J191" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K191" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L191" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M191" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N191" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O191" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P191" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="48" customHeight="1">
+      <x:c r="A192" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B192" s="66" t="str">
+        <x:v>PUSH_LADDER</x:v>
+      </x:c>
+      <x:c r="C192" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D192" s="66" t="str">
+        <x:v>Push the siege ladder away before more Uruk-hai reach the wall.</x:v>
+      </x:c>
+      <x:c r="E192" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F192" s="66" t="str">
+        <x:v>The ladder falls and isolates the Berserker beside Aragorn.</x:v>
+      </x:c>
+      <x:c r="G192" s="66" t="str">
+        <x:v>The ladder's hooks hold and the Berserker clears the parapet.</x:v>
+      </x:c>
+      <x:c r="H192" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I192" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J192" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K192" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L192" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M192" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N192" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O192" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P192" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="48" customHeight="1">
+      <x:c r="A193" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B193" s="66" t="str">
+        <x:v>HOLD_BREACH</x:v>
+      </x:c>
+      <x:c r="C193" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D193" s="66" t="str">
+        <x:v>Stand in the broken wall while Aragorn rallies the defenders.</x:v>
+      </x:c>
+      <x:c r="E193" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F193" s="66" t="str">
+        <x:v>You hold the narrow breach and absorb the first assault.</x:v>
+      </x:c>
+      <x:c r="G193" s="66" t="str">
+        <x:v>The Berserker drives you back into the courtyard.</x:v>
+      </x:c>
+      <x:c r="H193" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I193" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J193" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K193" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L193" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M193" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N193" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O193" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P193" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="48" customHeight="1">
+      <x:c r="A194" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B194" s="66" t="str">
+        <x:v>CROSS_PARAPET</x:v>
+      </x:c>
+      <x:c r="C194" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D194" s="66" t="str">
+        <x:v>Run the rain-slick parapet and strike from the tower side.</x:v>
+      </x:c>
+      <x:c r="E194" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F194" s="66" t="str">
+        <x:v>You reach the flank before the Berserker turns.</x:v>
+      </x:c>
+      <x:c r="G194" s="66" t="str">
+        <x:v>Your footing slips on the broken stone.</x:v>
+      </x:c>
+      <x:c r="H194" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I194" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J194" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K194" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L194" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M194" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N194" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O194" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P194" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="48" customHeight="1">
+      <x:c r="A195" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B195" s="66" t="str">
+        <x:v>CUT_ROPE</x:v>
+      </x:c>
+      <x:c r="C195" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D195" s="66" t="str">
+        <x:v>Cut one siege rope and gamble on which ladder it supports.</x:v>
+      </x:c>
+      <x:c r="E195" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F195" s="66" t="str">
+        <x:v>The correct ladder twists away and exposes the Berserker.</x:v>
+      </x:c>
+      <x:c r="G195" s="66" t="str">
+        <x:v>The rope belongs to a defender's barricade.</x:v>
+      </x:c>
+      <x:c r="H195" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I195" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J195" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K195" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L195" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M195" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N195" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O195" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P195" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="48" customHeight="1">
+      <x:c r="A196" s="66" t="str">
+        <x:v>TWOTOWERS_DEEPING_BREACH</x:v>
+      </x:c>
+      <x:c r="B196" s="66" t="str">
+        <x:v>SPOT_CHARGE</x:v>
+      </x:c>
+      <x:c r="C196" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D196" s="66" t="str">
+        <x:v>Identify the Berserker carrying the explosive charge through the rain.</x:v>
+      </x:c>
+      <x:c r="E196" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F196" s="66" t="str">
+        <x:v>You point out the threat and Aragorn intercepts it.</x:v>
+      </x:c>
+      <x:c r="G196" s="66" t="str">
+        <x:v>A decoy charge draws your warning away.</x:v>
+      </x:c>
+      <x:c r="H196" s="73" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I196" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J196" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K196" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L196" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M196" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N196" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O196" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P196" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="48" customHeight="1">
+      <x:c r="A197" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B197" s="66" t="str">
+        <x:v>BEND_MAST</x:v>
+      </x:c>
+      <x:c r="C197" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D197" s="66" t="str">
+        <x:v>Pull down the antenna mast across Jones's firing position.</x:v>
+      </x:c>
+      <x:c r="E197" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F197" s="66" t="str">
+        <x:v>The mast forces the Agent into Neo's line of attack.</x:v>
+      </x:c>
+      <x:c r="G197" s="66" t="str">
+        <x:v>Jones catches the falling structure and turns it aside.</x:v>
+      </x:c>
+      <x:c r="H197" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I197" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J197" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K197" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L197" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M197" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N197" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O197" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P197" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="48" customHeight="1">
+      <x:c r="A198" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B198" s="66" t="str">
+        <x:v>IGNORE_BULLETS</x:v>
+      </x:c>
+      <x:c r="C198" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D198" s="66" t="str">
+        <x:v>Keep moving despite the simulation's impact warnings.</x:v>
+      </x:c>
+      <x:c r="E198" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F198" s="66" t="str">
+        <x:v>You remain focused and hold Jones's attention.</x:v>
+      </x:c>
+      <x:c r="G198" s="66" t="str">
+        <x:v>The pain response overwhelms your concentration.</x:v>
+      </x:c>
+      <x:c r="H198" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I198" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J198" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K198" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L198" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M198" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N198" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O198" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P198" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="48" customHeight="1">
+      <x:c r="A199" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B199" s="66" t="str">
+        <x:v>ROOFTOP_LEAP</x:v>
+      </x:c>
+      <x:c r="C199" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D199" s="66" t="str">
+        <x:v>Leap the gap to the adjacent roof and attack from above.</x:v>
+      </x:c>
+      <x:c r="E199" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F199" s="66" t="str">
+        <x:v>You clear the gap and arrive beyond Jones's tracking arc.</x:v>
+      </x:c>
+      <x:c r="G199" s="66" t="str">
+        <x:v>The distance stretches as the Matrix resists you.</x:v>
+      </x:c>
+      <x:c r="H199" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I199" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J199" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K199" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L199" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M199" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N199" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O199" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P199" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="48" customHeight="1">
+      <x:c r="A200" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B200" s="66" t="str">
+        <x:v>ENTER_GLITCH</x:v>
+      </x:c>
+      <x:c r="C200" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D200" s="66" t="str">
+        <x:v>Step into a flickering service door before its destination stabilizes.</x:v>
+      </x:c>
+      <x:c r="E200" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F200" s="66" t="str">
+        <x:v>The glitch deposits you behind the Agent.</x:v>
+      </x:c>
+      <x:c r="G200" s="66" t="str">
+        <x:v>The door loops back into his sights.</x:v>
+      </x:c>
+      <x:c r="H200" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I200" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J200" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K200" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L200" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M200" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N200" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O200" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P200" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="48" customHeight="1">
+      <x:c r="A201" s="66" t="str">
+        <x:v>MATRIX_ROOFTOP_AGENT</x:v>
+      </x:c>
+      <x:c r="B201" s="66" t="str">
+        <x:v>SEE_POSSESSION</x:v>
+      </x:c>
+      <x:c r="C201" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D201" s="66" t="str">
+        <x:v>Watch the crowd below for the next body Jones intends to occupy.</x:v>
+      </x:c>
+      <x:c r="E201" s="73" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F201" s="66" t="str">
+        <x:v>You identify the transfer before it completes.</x:v>
+      </x:c>
+      <x:c r="G201" s="66" t="str">
+        <x:v>A harmless bystander flickers and draws your attention.</x:v>
+      </x:c>
+      <x:c r="H201" s="73" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I201" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J201" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K201" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L201" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M201" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N201" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O201" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P201" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="48" customHeight="1">
+      <x:c r="A202" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B202" s="66" t="str">
+        <x:v>BREAK_CHAIN</x:v>
+      </x:c>
+      <x:c r="C202" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D202" s="66" t="str">
+        <x:v>Wrench a tiger chain around Tigris's shield arm before the handler pulls it taut.</x:v>
+      </x:c>
+      <x:c r="E202" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F202" s="66" t="str">
+        <x:v>The chain binds shield to armor and opens Tigris to Maximus.</x:v>
+      </x:c>
+      <x:c r="G202" s="66" t="str">
+        <x:v>The tiger's lunge tears the chain out of your hands.</x:v>
+      </x:c>
+      <x:c r="H202" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I202" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J202" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K202" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L202" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M202" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N202" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O202" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P202" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="48" customHeight="1">
+      <x:c r="A203" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B203" s="66" t="str">
+        <x:v>MEET_CHARGE</x:v>
+      </x:c>
+      <x:c r="C203" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D203" s="66" t="str">
+        <x:v>Hold the center while chained tigers strike from both trapdoors.</x:v>
+      </x:c>
+      <x:c r="E203" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F203" s="66" t="str">
+        <x:v>You absorb the chaos and give Maximus room to face Tigris alone.</x:v>
+      </x:c>
+      <x:c r="G203" s="66" t="str">
+        <x:v>A tiger's impact drives you beneath Tigris's sword.</x:v>
+      </x:c>
+      <x:c r="H203" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I203" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J203" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K203" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L203" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M203" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N203" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O203" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P203" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="48" customHeight="1">
+      <x:c r="A204" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B204" s="66" t="str">
+        <x:v>ROLL_BLADE</x:v>
+      </x:c>
+      <x:c r="C204" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D204" s="66" t="str">
+        <x:v>Roll beneath Tigris's axe as a tiger crosses behind him.</x:v>
+      </x:c>
+      <x:c r="E204" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F204" s="66" t="str">
+        <x:v>You rise beyond the axe and force him toward the tiger chain.</x:v>
+      </x:c>
+      <x:c r="G204" s="66" t="str">
+        <x:v>The sand gives way above a trapdoor and ruins the roll.</x:v>
+      </x:c>
+      <x:c r="H204" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I204" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J204" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K204" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L204" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M204" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N204" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O204" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P204" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="48" customHeight="1">
+      <x:c r="A205" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B205" s="66" t="str">
+        <x:v>RELEASE_GATE</x:v>
+      </x:c>
+      <x:c r="C205" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D205" s="66" t="str">
+        <x:v>Cut one handler's rope and trust the tiger to charge the brighter armor.</x:v>
+      </x:c>
+      <x:c r="E205" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F205" s="66" t="str">
+        <x:v>The tiger turns on Tigris's polished silhouette and breaks his formation.</x:v>
+      </x:c>
+      <x:c r="G205" s="66" t="str">
+        <x:v>The animal follows your movement instead.</x:v>
+      </x:c>
+      <x:c r="H205" s="73" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I205" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J205" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K205" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L205" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M205" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N205" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O205" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P205" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="48" customHeight="1">
+      <x:c r="A206" s="66" t="str">
+        <x:v>GLADIATOR_TIGRIS_ARENA</x:v>
+      </x:c>
+      <x:c r="B206" s="66" t="str">
+        <x:v>READ_ARMOR</x:v>
+      </x:c>
+      <x:c r="C206" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D206" s="66" t="str">
+        <x:v>Watch the trapdoor sand for the tremor that precedes each tiger release.</x:v>
+      </x:c>
+      <x:c r="E206" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F206" s="66" t="str">
+        <x:v>You call the next opening and Maximus turns Tigris into the lunge.</x:v>
+      </x:c>
+      <x:c r="G206" s="66" t="str">
+        <x:v>The crowd's stamping hides the warning tremor.</x:v>
+      </x:c>
+      <x:c r="H206" s="73" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I206" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J206" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K206" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L206" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M206" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N206" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O206" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P206" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="48" customHeight="1">
+      <x:c r="A207" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B207" s="66" t="str">
+        <x:v>BAR_DOOR</x:v>
+      </x:c>
+      <x:c r="C207" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D207" s="66" t="str">
+        <x:v>Ram Blair's heavy tool cabinet across the tunnel mouth beneath the shed.</x:v>
+      </x:c>
+      <x:c r="E207" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F207" s="66" t="str">
+        <x:v>The cabinet seals the unfinished craft away from the infected crewman.</x:v>
+      </x:c>
+      <x:c r="G207" s="66" t="str">
+        <x:v>Something below lifts the cabinet as though it were empty.</x:v>
+      </x:c>
+      <x:c r="H207" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I207" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J207" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K207" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L207" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M207" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N207" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O207" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P207" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="48" customHeight="1">
+      <x:c r="A208" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B208" s="66" t="str">
+        <x:v>CROSS_BLIZZARD</x:v>
+      </x:c>
+      <x:c r="C208" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D208" s="66" t="str">
+        <x:v>Hold the flamethrower steady while the imitation cycles through familiar faces.</x:v>
+      </x:c>
+      <x:c r="E208" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F208" s="66" t="str">
+        <x:v>You resist the voices and keep the flame trained on the changing body.</x:v>
+      </x:c>
+      <x:c r="G208" s="66" t="str">
+        <x:v>A perfect imitation of a crewman's plea makes your aim falter.</x:v>
+      </x:c>
+      <x:c r="H208" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I208" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J208" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K208" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L208" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M208" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N208" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O208" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P208" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="48" customHeight="1">
+      <x:c r="A209" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B209" s="66" t="str">
+        <x:v>CLIMB_ROOF</x:v>
+      </x:c>
+      <x:c r="C209" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D209" s="66" t="str">
+        <x:v>Cross the rafters before a half-built mechanical limb reaches the ladder.</x:v>
+      </x:c>
+      <x:c r="E209" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F209" s="66" t="str">
+        <x:v>You reach the fuel drums and cut off the creature's escape.</x:v>
+      </x:c>
+      <x:c r="G209" s="66" t="str">
+        <x:v>The limb punches through the boards beneath your feet.</x:v>
+      </x:c>
+      <x:c r="H209" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I209" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J209" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K209" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L209" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M209" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N209" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O209" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P209" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="48" customHeight="1">
+      <x:c r="A210" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B210" s="66" t="str">
+        <x:v>CUT_FUEL</x:v>
+      </x:c>
+      <x:c r="C210" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D210" s="66" t="str">
+        <x:v>Throw a flare into the excavation and trust the fuel trail to reveal its route.</x:v>
+      </x:c>
+      <x:c r="E210" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F210" s="66" t="str">
+        <x:v>Fire races along the hidden tunnel and silhouettes the imitation.</x:v>
+      </x:c>
+      <x:c r="G210" s="66" t="str">
+        <x:v>The flare lands in snowmelt and leaves the tunnel dark.</x:v>
+      </x:c>
+      <x:c r="H210" s="73" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I210" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J210" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K210" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L210" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M210" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N210" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O210" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P210" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="48" customHeight="1">
+      <x:c r="A211" s="66" t="str">
+        <x:v>THING_GENERATOR_SHED</x:v>
+      </x:c>
+      <x:c r="B211" s="66" t="str">
+        <x:v>CHECK_BREATH</x:v>
+      </x:c>
+      <x:c r="C211" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D211" s="66" t="str">
+        <x:v>Compare the scavenged parts with the missing tractor and radio components.</x:v>
+      </x:c>
+      <x:c r="E211" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F211" s="66" t="str">
+        <x:v>The pattern reveals that the creature is assembling an escape craft below the shed.</x:v>
+      </x:c>
+      <x:c r="G211" s="66" t="str">
+        <x:v>The parts look like ordinary sabotage until the imitation moves.</x:v>
+      </x:c>
+      <x:c r="H211" s="73" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I211" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J211" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K211" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L211" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M211" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N211" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O211" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P211" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="48" customHeight="1">
+      <x:c r="A212" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B212" s="66" t="str">
+        <x:v>MOVE_CANNON</x:v>
+      </x:c>
+      <x:c r="C212" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D212" s="66" t="str">
+        <x:v>Drag a disabled cannon across the stormtrooper's firing lane.</x:v>
+      </x:c>
+      <x:c r="E212" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F212" s="66" t="str">
+        <x:v>The cannon forms cover and lets Luke advance.</x:v>
+      </x:c>
+      <x:c r="G212" s="66" t="str">
+        <x:v>The frozen mount locks before reaching the lane.</x:v>
+      </x:c>
+      <x:c r="H212" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I212" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J212" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K212" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L212" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M212" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N212" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O212" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P212" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="48" customHeight="1">
+      <x:c r="A213" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B213" s="66" t="str">
+        <x:v>CROSS_BLASTER_FIRE</x:v>
+      </x:c>
+      <x:c r="C213" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D213" s="66" t="str">
+        <x:v>Draw blaster fire while evacuees clear the junction.</x:v>
+      </x:c>
+      <x:c r="E213" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F213" s="66" t="str">
+        <x:v>You hold the corridor until Luke reaches the squad.</x:v>
+      </x:c>
+      <x:c r="G213" s="66" t="str">
+        <x:v>The barrage forces you against the blast door.</x:v>
+      </x:c>
+      <x:c r="H213" s="73" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I213" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J213" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K213" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L213" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M213" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N213" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O213" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P213" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="48" customHeight="1">
+      <x:c r="A214" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B214" s="66" t="str">
+        <x:v>ICE_TUNNEL</x:v>
+      </x:c>
+      <x:c r="C214" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D214" s="66" t="str">
+        <x:v>Take the narrow maintenance tunnel above the corridor.</x:v>
+      </x:c>
+      <x:c r="E214" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F214" s="66" t="str">
+        <x:v>You emerge behind the stormtrooper position.</x:v>
+      </x:c>
+      <x:c r="G214" s="66" t="str">
+        <x:v>Falling ice gives away the tunnel exit.</x:v>
+      </x:c>
+      <x:c r="H214" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I214" s="73" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J214" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K214" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L214" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M214" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N214" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O214" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P214" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="48" customHeight="1">
+      <x:c r="A215" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B215" s="66" t="str">
+        <x:v>FIRE_STEAM</x:v>
+      </x:c>
+      <x:c r="C215" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D215" s="66" t="str">
+        <x:v>Shoot a frozen pipe and gamble that it vents across the enemy.</x:v>
+      </x:c>
+      <x:c r="E215" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F215" s="66" t="str">
+        <x:v>Steam blinds the stormtrooper without blocking Luke.</x:v>
+      </x:c>
+      <x:c r="G215" s="66" t="str">
+        <x:v>The pipe vents across your own route.</x:v>
+      </x:c>
+      <x:c r="H215" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I215" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J215" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K215" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L215" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M215" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N215" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O215" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P215" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="48" customHeight="1">
+      <x:c r="A216" s="66" t="str">
+        <x:v>EMPIRE_ECHO_CORRIDOR</x:v>
+      </x:c>
+      <x:c r="B216" s="66" t="str">
+        <x:v>READ_HELMET</x:v>
+      </x:c>
+      <x:c r="C216" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D216" s="66" t="str">
+        <x:v>Watch the helmet movement to anticipate the squad's targeting calls.</x:v>
+      </x:c>
+      <x:c r="E216" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F216" s="66" t="str">
+        <x:v>You identify the next firing lane before it forms.</x:v>
+      </x:c>
+      <x:c r="G216" s="66" t="str">
+        <x:v>A false head turn sends you into the shot.</x:v>
+      </x:c>
+      <x:c r="H216" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I216" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J216" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K216" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L216" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M216" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N216" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O216" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P216" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="48" customHeight="1">
+      <x:c r="A217" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B217" s="66" t="str">
+        <x:v>HOLD_BRIDGE</x:v>
+      </x:c>
+      <x:c r="C217" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D217" s="66" t="str">
+        <x:v>Catch the champion's descending war club on the haft and drive him back from the rail.</x:v>
+      </x:c>
+      <x:c r="E217" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F217" s="66" t="str">
+        <x:v>The impact carries him across the landing bridge and wins Vultan's roar.</x:v>
+      </x:c>
+      <x:c r="G217" s="66" t="str">
+        <x:v>His wings turn the blocked strike into a crushing dive.</x:v>
+      </x:c>
+      <x:c r="H217" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I217" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J217" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K217" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L217" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M217" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N217" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O217" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P217" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="48" customHeight="1">
+      <x:c r="A218" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B218" s="66" t="str">
+        <x:v>FACE_WIND</x:v>
+      </x:c>
+      <x:c r="C218" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D218" s="66" t="str">
+        <x:v>Stand through the buffet of his wings without stepping beyond the painted challenge ring.</x:v>
+      </x:c>
+      <x:c r="E218" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F218" s="66" t="str">
+        <x:v>You remain inside the ring and earn the Hawkmen's respect.</x:v>
+      </x:c>
+      <x:c r="G218" s="66" t="str">
+        <x:v>The gale forces one heel across the boundary.</x:v>
+      </x:c>
+      <x:c r="H218" s="73" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I218" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J218" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K218" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L218" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M218" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N218" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O218" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P218" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="48" customHeight="1">
+      <x:c r="A219" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B219" s="66" t="str">
+        <x:v>SWING_CHAIN</x:v>
+      </x:c>
+      <x:c r="C219" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D219" s="66" t="str">
+        <x:v>Swing from a hanging feast-chain and meet the Hawkman at balcony height.</x:v>
+      </x:c>
+      <x:c r="E219" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F219" s="66" t="str">
+        <x:v>You intercept his dive in front of Vultan's throne.</x:v>
+      </x:c>
+      <x:c r="G219" s="66" t="str">
+        <x:v>He folds one wing and drops beneath your swing.</x:v>
+      </x:c>
+      <x:c r="H219" s="73" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I219" s="73" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J219" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K219" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L219" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M219" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N219" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O219" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P219" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="48" customHeight="1">
+      <x:c r="A220" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B220" s="66" t="str">
+        <x:v>JUMP_GLIDER</x:v>
+      </x:c>
+      <x:c r="C220" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D220" s="66" t="str">
+        <x:v>Leap from the cloud balcony and trust a passing rocket cycle to carry you back.</x:v>
+      </x:c>
+      <x:c r="E220" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F220" s="66" t="str">
+        <x:v>The cycle rises beneath you and turns the fall into a spectacular return.</x:v>
+      </x:c>
+      <x:c r="G220" s="66" t="str">
+        <x:v>It banks away toward Ming's distant patrols.</x:v>
+      </x:c>
+      <x:c r="H220" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I220" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J220" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K220" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L220" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M220" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N220" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O220" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P220" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="48" customHeight="1">
+      <x:c r="A221" s="66" t="str">
+        <x:v>FLASHGORDON_SKY_CITY</x:v>
+      </x:c>
+      <x:c r="B221" s="66" t="str">
+        <x:v>WATCH_FEATHERS</x:v>
+      </x:c>
+      <x:c r="C221" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D221" s="66" t="str">
+        <x:v>Watch the champion's wing joints for the twitch that begins a dive.</x:v>
+      </x:c>
+      <x:c r="E221" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F221" s="66" t="str">
+        <x:v>You move before he leaves the perch and take away his momentum.</x:v>
+      </x:c>
+      <x:c r="G221" s="66" t="str">
+        <x:v>Vultan's cheering masks the shift in the champion's feathers.</x:v>
+      </x:c>
+      <x:c r="H221" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I221" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J221" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K221" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L221" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M221" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N221" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O221" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P221" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="48" customHeight="1">
+      <x:c r="A222" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B222" s="66" t="str">
+        <x:v>TURN_WINCH</x:v>
+      </x:c>
+      <x:c r="C222" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D222" s="66" t="str">
+        <x:v>Turn the gate winch against its locking mechanism.</x:v>
+      </x:c>
+      <x:c r="E222" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F222" s="66" t="str">
+        <x:v>The chain moves and blocks the soldier's advance.</x:v>
+      </x:c>
+      <x:c r="G222" s="66" t="str">
+        <x:v>The winch catches and signals the guard.</x:v>
+      </x:c>
+      <x:c r="H222" s="73" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I222" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J222" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K222" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L222" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M222" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N222" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O222" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P222" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="48" customHeight="1">
+      <x:c r="A223" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B223" s="66" t="str">
+        <x:v>HOLD_PORTCULLIS</x:v>
+      </x:c>
+      <x:c r="C223" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D223" s="66" t="str">
+        <x:v>Hold the descending portcullis while Willow passes beneath it.</x:v>
+      </x:c>
+      <x:c r="E223" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F223" s="66" t="str">
+        <x:v>You endure the weight and keep the route open.</x:v>
+      </x:c>
+      <x:c r="G223" s="66" t="str">
+        <x:v>The iron teeth force you to release it.</x:v>
+      </x:c>
+      <x:c r="H223" s="73" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I223" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J223" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K223" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L223" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M223" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N223" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O223" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P223" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="48" customHeight="1">
+      <x:c r="A224" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B224" s="66" t="str">
+        <x:v>CLIMB_CHAIN</x:v>
+      </x:c>
+      <x:c r="C224" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D224" s="66" t="str">
+        <x:v>Climb the gate chain and enter through the upper mechanism.</x:v>
+      </x:c>
+      <x:c r="E224" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F224" s="66" t="str">
+        <x:v>You reach the stair above the soldier.</x:v>
+      </x:c>
+      <x:c r="G224" s="66" t="str">
+        <x:v>The chain swings against the stone and alerts him.</x:v>
+      </x:c>
+      <x:c r="H224" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I224" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J224" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K224" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L224" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M224" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N224" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O224" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P224" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="48" customHeight="1">
+      <x:c r="A225" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B225" s="66" t="str">
+        <x:v>USE_ACORN</x:v>
+      </x:c>
+      <x:c r="C225" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D225" s="66" t="str">
+        <x:v>Cast an enchanted acorn at the gate and trust what it transforms.</x:v>
+      </x:c>
+      <x:c r="E225" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F225" s="66" t="str">
+        <x:v>The locking bar turns to stone and snaps under its own weight.</x:v>
+      </x:c>
+      <x:c r="G225" s="66" t="str">
+        <x:v>The acorn transforms a harmless support instead.</x:v>
+      </x:c>
+      <x:c r="H225" s="73" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I225" s="73" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J225" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K225" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L225" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M225" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N225" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O225" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P225" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="48" customHeight="1">
+      <x:c r="A226" s="66" t="str">
+        <x:v>WILLOW_NOCKMAAR_GATE</x:v>
+      </x:c>
+      <x:c r="B226" s="66" t="str">
+        <x:v>READ_CREST</x:v>
+      </x:c>
+      <x:c r="C226" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D226" s="66" t="str">
+        <x:v>Study the guard crests to identify the captain's control key.</x:v>
+      </x:c>
+      <x:c r="E226" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F226" s="66" t="str">
+        <x:v>The correct insignia reveals which key opens the gate.</x:v>
+      </x:c>
+      <x:c r="G226" s="66" t="str">
+        <x:v>A ceremonial crest points to the wrong ring.</x:v>
+      </x:c>
+      <x:c r="H226" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I226" s="73" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J226" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K226" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L226" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M226" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N226" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O226" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P226" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="48" customHeight="1">
+      <x:c r="A227" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B227" s="66" t="str">
+        <x:v>MOVE_WALL</x:v>
+      </x:c>
+      <x:c r="C227" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D227" s="66" t="str">
+        <x:v>Push the rotating wall before the goblin seals the passage.</x:v>
+      </x:c>
+      <x:c r="E227" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F227" s="66" t="str">
+        <x:v>The wall turns and traps the guard on Sarah's side.</x:v>
+      </x:c>
+      <x:c r="G227" s="66" t="str">
+        <x:v>The mechanism reverses and opens beside him.</x:v>
+      </x:c>
+      <x:c r="H227" s="73" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I227" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J227" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K227" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L227" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M227" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N227" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O227" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P227" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="48" customHeight="1">
+      <x:c r="A228" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B228" s="66" t="str">
+        <x:v>IGNORE_RIDDLES</x:v>
+      </x:c>
+      <x:c r="C228" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D228" s="66" t="str">
+        <x:v>Keep walking as the corridor repeats the same taunts and turns.</x:v>
+      </x:c>
+      <x:c r="E228" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F228" s="66" t="str">
+        <x:v>You resist the maze and maintain the true direction.</x:v>
+      </x:c>
+      <x:c r="G228" s="66" t="str">
+        <x:v>The repetition breaks your focus and the guard catches up.</x:v>
+      </x:c>
+      <x:c r="H228" s="73" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I228" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J228" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K228" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L228" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M228" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N228" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O228" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P228" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="48" customHeight="1">
+      <x:c r="A229" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B229" s="66" t="str">
+        <x:v>CLIMB_DOORS</x:v>
+      </x:c>
+      <x:c r="C229" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D229" s="66" t="str">
+        <x:v>Climb the stacked doorframes and cross above the patrol.</x:v>
+      </x:c>
+      <x:c r="E229" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F229" s="66" t="str">
+        <x:v>You descend behind the Goblin Guard.</x:v>
+      </x:c>
+      <x:c r="G229" s="66" t="str">
+        <x:v>A painted door swings open beneath your hand.</x:v>
+      </x:c>
+      <x:c r="H229" s="73" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I229" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J229" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K229" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L229" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M229" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N229" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O229" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P229" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="48" customHeight="1">
+      <x:c r="A230" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B230" s="66" t="str">
+        <x:v>CHOOSE_KNOCKER</x:v>
+      </x:c>
+      <x:c r="C230" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D230" s="66" t="str">
+        <x:v>Use one of two arguing door knockers without resolving which tells the truth.</x:v>
+      </x:c>
+      <x:c r="E230" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F230" s="66" t="str">
+        <x:v>The chosen door opens onto the guard's blind side.</x:v>
+      </x:c>
+      <x:c r="G230" s="66" t="str">
+        <x:v>It opens directly in front of his patrol.</x:v>
+      </x:c>
+      <x:c r="H230" s="73" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I230" s="73" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J230" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K230" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L230" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M230" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N230" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O230" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P230" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="48" customHeight="1">
+      <x:c r="A231" s="66" t="str">
+        <x:v>LABYRINTH_GOBLIN_PATROL</x:v>
+      </x:c>
+      <x:c r="B231" s="66" t="str">
+        <x:v>FOLLOW_CHALK</x:v>
+      </x:c>
+      <x:c r="C231" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D231" s="66" t="str">
+        <x:v>Separate Sarah's chalk marks from the copies made by the maze.</x:v>
+      </x:c>
+      <x:c r="E231" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F231" s="66" t="str">
+        <x:v>The smudged original reveals the real route.</x:v>
+      </x:c>
+      <x:c r="G231" s="66" t="str">
+        <x:v>A perfect imitation leads toward the guard.</x:v>
+      </x:c>
+      <x:c r="H231" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I231" s="73" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J231" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K231" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L231" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M231" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N231" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O231" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P231" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="48" customHeight="1">
+      <x:c r="A232" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B232" s="66" t="str">
+        <x:v>BREAK_WALL</x:v>
+      </x:c>
+      <x:c r="C232" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D232" s="66" t="str">
+        <x:v>Drive a disc into the arena wall until its code fractures.</x:v>
+      </x:c>
+      <x:c r="E232" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F232" s="66" t="str">
+        <x:v>The wall opens and limits Sark's movement.</x:v>
+      </x:c>
+      <x:c r="G232" s="66" t="str">
+        <x:v>The disc rebounds into his attack path.</x:v>
+      </x:c>
+      <x:c r="H232" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I232" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J232" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K232" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L232" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M232" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N232" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O232" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P232" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="48" customHeight="1">
+      <x:c r="A233" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B233" s="66" t="str">
+        <x:v>ABSORB_IMPACT</x:v>
+      </x:c>
+      <x:c r="C233" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D233" s="66" t="str">
+        <x:v>Take Sark's first disc impact and keep Flynn's platform active.</x:v>
+      </x:c>
+      <x:c r="E233" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F233" s="66" t="str">
+        <x:v>You remain coherent and preserve the platform.</x:v>
+      </x:c>
+      <x:c r="G233" s="66" t="str">
+        <x:v>The impact destabilizes your code.</x:v>
+      </x:c>
+      <x:c r="H233" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I233" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J233" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K233" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L233" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M233" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N233" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O233" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P233" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="48" customHeight="1">
+      <x:c r="A234" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B234" s="66" t="str">
+        <x:v>JUMP_GRID</x:v>
+      </x:c>
+      <x:c r="C234" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D234" s="66" t="str">
+        <x:v>Leap between disappearing grid squares and reach Sark's platform.</x:v>
+      </x:c>
+      <x:c r="E234" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F234" s="66" t="str">
+        <x:v>You cross before the sequence resets.</x:v>
+      </x:c>
+      <x:c r="G234" s="66" t="str">
+        <x:v>A square vanishes beneath your landing.</x:v>
+      </x:c>
+      <x:c r="H234" s="73" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I234" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J234" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K234" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L234" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M234" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N234" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O234" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P234" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="48" customHeight="1">
+      <x:c r="A235" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B235" s="66" t="str">
+        <x:v>THROW_BANK</x:v>
+      </x:c>
+      <x:c r="C235" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D235" s="66" t="str">
+        <x:v>Bank a disc off an untested wall angle.</x:v>
+      </x:c>
+      <x:c r="E235" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F235" s="66" t="str">
+        <x:v>The ricochet strikes Sark from outside his guard.</x:v>
+      </x:c>
+      <x:c r="G235" s="66" t="str">
+        <x:v>The angle returns the disc toward you.</x:v>
+      </x:c>
+      <x:c r="H235" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I235" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J235" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K235" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L235" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M235" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N235" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O235" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P235" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="48" customHeight="1">
+      <x:c r="A236" s="66" t="str">
+        <x:v>TRON_DISC_ARENA</x:v>
+      </x:c>
+      <x:c r="B236" s="66" t="str">
+        <x:v>READ_PATTERN</x:v>
+      </x:c>
+      <x:c r="C236" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D236" s="66" t="str">
+        <x:v>Study the arena pulse to predict which grid squares will remain.</x:v>
+      </x:c>
+      <x:c r="E236" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F236" s="66" t="str">
+        <x:v>The pattern reveals a stable path to Sark.</x:v>
+      </x:c>
+      <x:c r="G236" s="66" t="str">
+        <x:v>The MCP changes the sequence after you commit.</x:v>
+      </x:c>
+      <x:c r="H236" s="73" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I236" s="73" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J236" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K236" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L236" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M236" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N236" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O236" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P236" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="48" customHeight="1">
+      <x:c r="A237" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B237" s="66" t="str">
+        <x:v>SLAM_COFFIN</x:v>
+      </x:c>
+      <x:c r="C237" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D237" s="66" t="str">
+        <x:v>Slam a coffin lid across the Deadite's path.</x:v>
+      </x:c>
+      <x:c r="E237" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F237" s="66" t="str">
+        <x:v>The lid pins the warrior long enough for Ash to aim.</x:v>
+      </x:c>
+      <x:c r="G237" s="66" t="str">
+        <x:v>The rotten wood bursts apart in your hands.</x:v>
+      </x:c>
+      <x:c r="H237" s="73" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I237" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J237" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K237" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L237" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M237" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N237" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O237" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P237" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="48" customHeight="1">
+      <x:c r="A238" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B238" s="66" t="str">
+        <x:v>IGNORE_BITE</x:v>
+      </x:c>
+      <x:c r="C238" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D238" s="66" t="str">
+        <x:v>Hold the Deadite back despite its claws and teeth.</x:v>
+      </x:c>
+      <x:c r="E238" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F238" s="66" t="str">
+        <x:v>You keep it occupied and refuse to release your grip.</x:v>
+      </x:c>
+      <x:c r="G238" s="66" t="str">
+        <x:v>Its relentless attack breaks your hold.</x:v>
+      </x:c>
+      <x:c r="H238" s="73" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I238" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J238" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K238" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L238" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M238" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N238" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O238" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P238" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="48" customHeight="1">
+      <x:c r="A239" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B239" s="66" t="str">
+        <x:v>SWING_SHOVEL</x:v>
+      </x:c>
+      <x:c r="C239" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D239" s="66" t="str">
+        <x:v>Vault a gravestone and seize the shovel behind the Deadite.</x:v>
+      </x:c>
+      <x:c r="E239" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F239" s="66" t="str">
+        <x:v>You land with the weapon at its exposed back.</x:v>
+      </x:c>
+      <x:c r="G239" s="66" t="str">
+        <x:v>The stone tips and drops you into the grave.</x:v>
+      </x:c>
+      <x:c r="H239" s="73" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I239" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J239" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K239" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L239" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M239" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N239" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O239" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P239" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="48" customHeight="1">
+      <x:c r="A240" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B240" s="66" t="str">
+        <x:v>RECITE_WORDS</x:v>
+      </x:c>
+      <x:c r="C240" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D240" s="66" t="str">
+        <x:v>Recite the half-remembered burial phrase and hope it is close enough.</x:v>
+      </x:c>
+      <x:c r="E240" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F240" s="66" t="str">
+        <x:v>The ground grips the Deadite's legs and halts it.</x:v>
+      </x:c>
+      <x:c r="G240" s="66" t="str">
+        <x:v>The wrong words awaken another burst of movement.</x:v>
+      </x:c>
+      <x:c r="H240" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I240" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J240" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K240" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L240" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M240" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N240" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O240" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P240" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="48" customHeight="1">
+      <x:c r="A241" s="66" t="str">
+        <x:v>ARMYDARKNESS_GRAVEYARD</x:v>
+      </x:c>
+      <x:c r="B241" s="66" t="str">
+        <x:v>CHECK_SHADOW</x:v>
+      </x:c>
+      <x:c r="C241" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D241" s="66" t="str">
+        <x:v>Use the moonlight to distinguish the moving corpse from the still ones.</x:v>
+      </x:c>
+      <x:c r="E241" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F241" s="66" t="str">
+        <x:v>The wrong shadow reveals the Deadite before it lunges.</x:v>
+      </x:c>
+      <x:c r="G241" s="66" t="str">
+        <x:v>A swaying branch creates a convincing false target.</x:v>
+      </x:c>
+      <x:c r="H241" s="73" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I241" s="73" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J241" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K241" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L241" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M241" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N241" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O241" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P241" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="48" customHeight="1">
+      <x:c r="A242" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B242" s="66" t="str">
+        <x:v>TOPPLE_COLUMN</x:v>
+      </x:c>
+      <x:c r="C242" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D242" s="66" t="str">
+        <x:v>Topple a cracked column across the guard's route.</x:v>
+      </x:c>
+      <x:c r="E242" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F242" s="66" t="str">
+        <x:v>The column falls and traps the Horus Guard in the courtyard.</x:v>
+      </x:c>
+      <x:c r="G242" s="66" t="str">
+        <x:v>The stone turns and falls away from the target.</x:v>
+      </x:c>
+      <x:c r="H242" s="73" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I242" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J242" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K242" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L242" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M242" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N242" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O242" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P242" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="48" customHeight="1">
+      <x:c r="A243" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B243" s="66" t="str">
+        <x:v>CROSS_STAFF_FIRE</x:v>
+      </x:c>
+      <x:c r="C243" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D243" s="66" t="str">
+        <x:v>Advance through staff blasts while Daniel reaches the glyphs.</x:v>
+      </x:c>
+      <x:c r="E243" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F243" s="66" t="str">
+        <x:v>You endure the fire and keep the guard focused on you.</x:v>
+      </x:c>
+      <x:c r="G243" s="66" t="str">
+        <x:v>The barrage halts you short of the doorway.</x:v>
+      </x:c>
+      <x:c r="H243" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I243" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J243" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K243" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L243" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M243" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N243" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O243" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P243" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="48" customHeight="1">
+      <x:c r="A244" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B244" s="66" t="str">
+        <x:v>CLIMB_STATUE</x:v>
+      </x:c>
+      <x:c r="C244" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D244" s="66" t="str">
+        <x:v>Climb the temple statue and descend behind the guard.</x:v>
+      </x:c>
+      <x:c r="E244" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F244" s="66" t="str">
+        <x:v>You land beyond the helmet's field of view.</x:v>
+      </x:c>
+      <x:c r="G244" s="66" t="str">
+        <x:v>Loose ornament crashes into the courtyard.</x:v>
+      </x:c>
+      <x:c r="H244" s="73" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I244" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J244" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K244" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L244" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M244" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N244" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O244" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P244" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="48" customHeight="1">
+      <x:c r="A245" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B245" s="66" t="str">
+        <x:v>PRESS_SYMBOL</x:v>
+      </x:c>
+      <x:c r="C245" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D245" s="66" t="str">
+        <x:v>Press an unknown wall symbol and gamble that it controls the gate.</x:v>
+      </x:c>
+      <x:c r="E245" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F245" s="66" t="str">
+        <x:v>The gate shifts and separates the guard from reinforcements.</x:v>
+      </x:c>
+      <x:c r="G245" s="66" t="str">
+        <x:v>The symbol activates a warning beacon.</x:v>
+      </x:c>
+      <x:c r="H245" s="73" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I245" s="73" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J245" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K245" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L245" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M245" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N245" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O245" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P245" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="48" customHeight="1">
+      <x:c r="A246" s="66" t="str">
+        <x:v>STARGATE_TEMPLE_GATE</x:v>
+      </x:c>
+      <x:c r="B246" s="66" t="str">
+        <x:v>TRANSLATE_COMMAND</x:v>
+      </x:c>
+      <x:c r="C246" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D246" s="66" t="str">
+        <x:v>Translate the cartouche on the guard's control bracer.</x:v>
+      </x:c>
+      <x:c r="E246" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F246" s="66" t="str">
+        <x:v>You identify the symbol that interrupts its weapon.</x:v>
+      </x:c>
+      <x:c r="G246" s="66" t="str">
+        <x:v>A ceremonial inscription conceals the real command.</x:v>
+      </x:c>
+      <x:c r="H246" s="73" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I246" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J246" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K246" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L246" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M246" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N246" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O246" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P246" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="48" customHeight="1">
+      <x:c r="A247" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B247" s="66" t="str">
+        <x:v>BREAK_LANCE</x:v>
+      </x:c>
+      <x:c r="C247" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D247" s="66" t="str">
+        <x:v>Catch the Black Knight's lance beneath your shield and wrench him from the saddle.</x:v>
+      </x:c>
+      <x:c r="E247" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F247" s="66" t="str">
+        <x:v>The lance locks against the shield rim and the knight crashes into the ford.</x:v>
+      </x:c>
+      <x:c r="G247" s="66" t="str">
+        <x:v>The charge drives shield and rider together through the water.</x:v>
+      </x:c>
+      <x:c r="H247" s="73" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I247" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J247" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K247" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L247" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M247" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N247" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O247" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P247" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="48" customHeight="1">
+      <x:c r="A248" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B248" s="66" t="str">
+        <x:v>HOLD_CROSSING</x:v>
+      </x:c>
+      <x:c r="C248" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D248" s="66" t="str">
+        <x:v>Stand knee-deep in the ford and refuse the full weight of his charge.</x:v>
+      </x:c>
+      <x:c r="E248" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F248" s="66" t="str">
+        <x:v>You hold the crossing long enough for Arthur to draw Excalibur.</x:v>
+      </x:c>
+      <x:c r="G248" s="66" t="str">
+        <x:v>The current and the horse's impact carry you downstream.</x:v>
+      </x:c>
+      <x:c r="H248" s="73" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I248" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J248" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K248" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L248" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M248" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N248" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O248" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P248" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="48" customHeight="1">
+      <x:c r="A249" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B249" s="66" t="str">
+        <x:v>VAULT_RAIL</x:v>
+      </x:c>
+      <x:c r="C249" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D249" s="66" t="str">
+        <x:v>Step onto the ruined causeway and slip inside the lance point.</x:v>
+      </x:c>
+      <x:c r="E249" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F249" s="66" t="str">
+        <x:v>You pass the point and reach the knight's unguarded rein hand.</x:v>
+      </x:c>
+      <x:c r="G249" s="66" t="str">
+        <x:v>A moss-covered stone turns under your foot.</x:v>
+      </x:c>
+      <x:c r="H249" s="73" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I249" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J249" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K249" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L249" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M249" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N249" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O249" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P249" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="48" customHeight="1">
+      <x:c r="A250" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B250" s="66" t="str">
+        <x:v>CHALLENGE_OATH</x:v>
+      </x:c>
+      <x:c r="C250" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D250" s="66" t="str">
+        <x:v>Answer his challenge with an older oath and gamble that his heraldry still binds him.</x:v>
+      </x:c>
+      <x:c r="E250" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F250" s="66" t="str">
+        <x:v>The knight pauses to return the oath, giving Arthur the first clean opening.</x:v>
+      </x:c>
+      <x:c r="G250" s="66" t="str">
+        <x:v>The banner was stolen, and the oath means nothing to him.</x:v>
+      </x:c>
+      <x:c r="H250" s="73" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I250" s="73" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J250" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K250" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L250" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M250" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N250" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O250" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P250" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="48" customHeight="1">
+      <x:c r="A251" s="66" t="str">
+        <x:v>EXCALIBUR_BLACK_BRIDGE</x:v>
+      </x:c>
+      <x:c r="B251" s="66" t="str">
+        <x:v>READ_HERALDRY</x:v>
+      </x:c>
+      <x:c r="C251" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D251" s="66" t="str">
+        <x:v>Read the ford's ripples to find where his armored horse must slow.</x:v>
+      </x:c>
+      <x:c r="E251" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F251" s="66" t="str">
+        <x:v>You mark the deep channel and Arthur meets the charge at its weakest point.</x:v>
+      </x:c>
+      <x:c r="G251" s="66" t="str">
+        <x:v>The morning wind disguises the dangerous shallows.</x:v>
+      </x:c>
+      <x:c r="H251" s="73" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I251" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J251" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K251" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L251" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M251" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N251" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O251" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P251" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="48" customHeight="1">
+      <x:c r="A252" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B252" s="66" t="str">
+        <x:v>SHIFT_WRECK</x:v>
+      </x:c>
+      <x:c r="C252" s="66" t="str">
+        <x:v>STR</x:v>
+      </x:c>
+      <x:c r="D252" s="66" t="str">
+        <x:v>Shift the ornithopter wreckage into the Sardaukar's descent.</x:v>
+      </x:c>
+      <x:c r="E252" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F252" s="66" t="str">
+        <x:v>The metal slides and forces the trooper into Paul's reach.</x:v>
+      </x:c>
+      <x:c r="G252" s="66" t="str">
+        <x:v>The wreck settles deeper into the sand.</x:v>
+      </x:c>
+      <x:c r="H252" s="73" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I252" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J252" s="66" t="str">
+        <x:v>FIRST_STRIKE</x:v>
+      </x:c>
+      <x:c r="K252" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L252" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M252" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N252" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O252" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P252" s="66" t="str">
+        <x:v>Strength approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="48" customHeight="1">
+      <x:c r="A253" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B253" s="66" t="str">
+        <x:v>CONTROL_WATER</x:v>
+      </x:c>
+      <x:c r="C253" s="66" t="str">
+        <x:v>END</x:v>
+      </x:c>
+      <x:c r="D253" s="66" t="str">
+        <x:v>Control your breathing and movement through the exhausting heat.</x:v>
+      </x:c>
+      <x:c r="E253" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F253" s="66" t="str">
+        <x:v>You conserve strength and hold the line beside Paul.</x:v>
+      </x:c>
+      <x:c r="G253" s="66" t="str">
+        <x:v>The heat drains your reactions before the attack.</x:v>
+      </x:c>
+      <x:c r="H253" s="73" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I253" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J253" s="66" t="str">
+        <x:v>ALLY_BUFF</x:v>
+      </x:c>
+      <x:c r="K253" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L253" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M253" s="66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N253" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O253" s="74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P253" s="66" t="str">
+        <x:v>Endurance approach; failure may cause opening damage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="48" customHeight="1">
+      <x:c r="A254" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B254" s="66" t="str">
+        <x:v>SANDWALK_FLANK</x:v>
+      </x:c>
+      <x:c r="C254" s="66" t="str">
+        <x:v>AGI</x:v>
+      </x:c>
+      <x:c r="D254" s="66" t="str">
+        <x:v>Use an irregular sandwalk to circle beyond the trooper's sight.</x:v>
+      </x:c>
+      <x:c r="E254" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F254" s="66" t="str">
+        <x:v>You reach the flank without creating a readable rhythm.</x:v>
+      </x:c>
+      <x:c r="G254" s="66" t="str">
+        <x:v>One repeated step reveals your path.</x:v>
+      </x:c>
+      <x:c r="H254" s="73" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I254" s="73" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J254" s="66" t="str">
+        <x:v>COMBAT_ADVANTAGE</x:v>
+      </x:c>
+      <x:c r="K254" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L254" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M254" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N254" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O254" s="74" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="P254" s="66" t="str">
+        <x:v>Agility approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="48" customHeight="1">
+      <x:c r="A255" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B255" s="66" t="str">
+        <x:v>TRUST_VISION</x:v>
+      </x:c>
+      <x:c r="C255" s="66" t="str">
+        <x:v>LCK</x:v>
+      </x:c>
+      <x:c r="D255" s="66" t="str">
+        <x:v>Follow a brief prescient image without knowing which future it belongs to.</x:v>
+      </x:c>
+      <x:c r="E255" s="73" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F255" s="66" t="str">
+        <x:v>The vision leads you through the blade's exact opening.</x:v>
+      </x:c>
+      <x:c r="G255" s="66" t="str">
+        <x:v>The possible future dissolves as you commit.</x:v>
+      </x:c>
+      <x:c r="H255" s="73" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I255" s="73" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J255" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K255" s="66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L255" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M255" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N255" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O255" s="74" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="P255" s="66" t="str">
+        <x:v>High-risk luck approach.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="48" customHeight="1">
+      <x:c r="A256" s="66" t="str">
+        <x:v>DUNE_SARDAUKAR_RAID</x:v>
+      </x:c>
+      <x:c r="B256" s="66" t="str">
+        <x:v>READ_BLADE</x:v>
+      </x:c>
+      <x:c r="C256" s="66" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="D256" s="66" t="str">
+        <x:v>Watch the Sardaukar's blade angle for the killing feint.</x:v>
+      </x:c>
+      <x:c r="E256" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F256" s="66" t="str">
+        <x:v>You identify the hidden second strike and warn Paul.</x:v>
+      </x:c>
+      <x:c r="G256" s="66" t="str">
+        <x:v>The trooper changes grip inside the motion.</x:v>
+      </x:c>
+      <x:c r="H256" s="73" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I256" s="73" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J256" s="66" t="str">
+        <x:v>ENEMY_DEBUFF</x:v>
+      </x:c>
+      <x:c r="K256" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L256" s="66" t="str">
+        <x:v>COMBAT</x:v>
+      </x:c>
+      <x:c r="M256" s="66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N256" s="67" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O256" s="74" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="P256" s="66" t="str">
+        <x:v>Perception approach.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd05973ff05a4d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8638799636be4922"/>
   </x:tableParts>
 </x:worksheet>
 </file>
